--- a/data/trans_camb/IP16B08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Edad-trans_camb.xlsx
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,92</t>
+          <t>0,0; 54,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,92</t>
+          <t>0,0; 54,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,55</t>
+          <t>0,0; 32,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,39</t>
+          <t>0,0; 28,07</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 121,82</t>
+          <t>0,0; 120,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 121,82</t>
+          <t>0,0; 120,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,16</t>
+          <t>0,0; 47,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,93</t>
+          <t>0,0; 39,15</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,85</t>
+          <t>0,0; 48,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,53</t>
+          <t>0,0; 55,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 0,0</t>
+          <t>-48,45; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 12,02</t>
+          <t>-24,25; 12,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,39</t>
+          <t>0,0; 33,03</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1019,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 99,4</t>
+          <t>0,0; 94,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 99,13</t>
+          <t>0,0; 127,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 0,0</t>
+          <t>-48,45; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 13,62</t>
+          <t>-25,42; 14,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,97</t>
+          <t>0,0; 49,34</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,84</t>
+          <t>0,0; 48,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,34</t>
+          <t>0,0; 44,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,99</t>
+          <t>0,0; 22,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,71</t>
+          <t>0,0; 26,99</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,27</t>
+          <t>0,0; 96,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 109,78</t>
+          <t>0,0; 79,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,91</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,77</t>
+          <t>0,0; 37,3</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,68</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 20,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 6,91</t>
+          <t>-20,88; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,4</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,72</t>
+          <t>-6,86; 9,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,05</t>
+          <t>1,51; 12,32</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,08</t>
+          <t>0,0; 26,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 26,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 7,42</t>
+          <t>-21,3; 7,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,61</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 9,68</t>
+          <t>-6,97; 10,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,54; 15,0</t>
+          <t>1,53; 14,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B08-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Edad-trans_camb.xlsx
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,62</t>
+          <t>0,0; 54,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,62</t>
+          <t>0,0; 54,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,37</t>
+          <t>0,0; 32,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,07</t>
+          <t>0,0; 27,98</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 120,36</t>
+          <t>0,0; 120,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 120,36</t>
+          <t>0,0; 120,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,86</t>
+          <t>0,0; 48,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,15</t>
+          <t>0,0; 38,92</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,55</t>
+          <t>0,0; 53,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,66</t>
+          <t>0,0; 50,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 0,0</t>
+          <t>-48,13; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 12,39</t>
+          <t>-29,49; 12,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,03</t>
+          <t>0,0; 27,87</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1019,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 94,36</t>
+          <t>0,0; 115,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 127,8</t>
+          <t>0,0; 103,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 0,0</t>
+          <t>-48,13; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 14,14</t>
+          <t>-30,27; 13,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,34</t>
+          <t>0,0; 38,67</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,97</t>
+          <t>0,0; 53,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,25</t>
+          <t>0,0; 53,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,39</t>
+          <t>0,0; 21,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,99</t>
+          <t>0,0; 17,74</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 96,53</t>
+          <t>0,0; 115,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,36</t>
+          <t>0,0; 115,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,86</t>
+          <t>0,0; 26,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,3</t>
+          <t>0,0; 21,57</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,74</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 6,95</t>
+          <t>-19,6; 6,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 17,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 9,44</t>
+          <t>-6,8; 9,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,32</t>
+          <t>1,48; 12,48</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,4</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,17</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 7,45</t>
+          <t>-20,91; 7,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 10,49</t>
+          <t>-6,94; 10,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,04</t>
+          <t>1,5; 14,25</t>
         </is>
       </c>
     </row>
